--- a/docs/ai_log/AI_AuditLog_TranQuocThinh_QE190140.xlsx
+++ b/docs/ai_log/AI_AuditLog_TranQuocThinh_QE190140.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\OneDrive\Máy tính\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6144ABD0-F88B-46C7-8086-8B3979FEA7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC139A7F-8349-49B8-898E-31BF16B4ED6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="186">
   <si>
     <t>AI AUDIT LOG — METADATA &amp; SUMMARY</t>
   </si>
@@ -154,9 +154,6 @@
   </si>
   <si>
     <t>DETAILED AI AUDIT LOG — Smart Hospital Patient Triage System (Hash Table Analysis)</t>
-  </si>
-  <si>
-    <t>INSTRUCTIONS: Chỉ ghi CORE PROMPTS (Decision/Problem-Solving/Verification). Mỗi entry phải trả lời đầy đủ 4 câu hỏi trong Human Delta.</t>
   </si>
   <si>
     <t>Entry #</t>
@@ -921,7 +918,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -977,24 +974,21 @@
     <xf numFmtId="0" fontId="6" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1016,6 +1010,10 @@
     <xf numFmtId="0" fontId="2" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1331,66 +1329,66 @@
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
     </row>
     <row r="8" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -1453,12 +1451,12 @@
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
@@ -1551,458 +1549,458 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="32" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="25.44140625" customWidth="1"/>
+    <col min="5" max="5" width="24.5546875" customWidth="1"/>
+    <col min="6" max="6" width="26.109375" customWidth="1"/>
+    <col min="7" max="7" width="24.44140625" customWidth="1"/>
+    <col min="8" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="18.5546875" customWidth="1"/>
+    <col min="11" max="11" width="21.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-    </row>
-    <row r="2" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+    </row>
+    <row r="2" spans="1:11" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="33"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K3" s="8" t="s">
+    </row>
+    <row r="4" spans="1:11" ht="159" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="B4" s="9" t="s">
         <v>56</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>57</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>33</v>
       </c>
       <c r="D4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="H4" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="J4" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="K4" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="K4" s="11" t="s">
+    </row>
+    <row r="5" spans="1:11" ht="137.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>66</v>
-      </c>
       <c r="B5" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="F5" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="G5" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="H5" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="I5" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="J5" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="K5" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="K5" s="11" t="s">
+    </row>
+    <row r="6" spans="1:11" ht="157.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="B6" s="12" t="s">
         <v>75</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>76</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>40</v>
       </c>
       <c r="D6" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="F6" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="G6" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="H6" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="I6" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="J6" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="K6" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="K6" s="11" t="s">
+    </row>
+    <row r="7" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25" t="s">
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+    </row>
+    <row r="8" spans="1:11" ht="142.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-    </row>
-    <row r="8" spans="1:11" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+      <c r="B8" s="13" t="s">
         <v>86</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>87</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>40</v>
       </c>
       <c r="D8" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="G8" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="H8" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="I8" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="J8" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="K8" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="K8" s="11" t="s">
+    </row>
+    <row r="9" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25" t="s">
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+    </row>
+    <row r="10" spans="1:11" ht="157.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-    </row>
-    <row r="10" spans="1:11" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>97</v>
-      </c>
       <c r="B10" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D10" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="F10" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="G10" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="H10" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="I10" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="J10" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="K10" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="K10" s="11" t="s">
+    </row>
+    <row r="11" spans="1:11" ht="160.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
-        <v>106</v>
-      </c>
       <c r="B11" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>40</v>
       </c>
       <c r="D11" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="F11" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="G11" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="H11" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="I11" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="J11" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="K11" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="K11" s="11" t="s">
+    </row>
+    <row r="12" spans="1:11" ht="147" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
-        <v>115</v>
-      </c>
       <c r="B12" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>36</v>
       </c>
       <c r="D12" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="F12" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="G12" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="H12" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="I12" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="J12" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="K12" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="K12" s="11" t="s">
+    </row>
+    <row r="13" spans="1:11" ht="125.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
-        <v>124</v>
-      </c>
       <c r="B13" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>33</v>
       </c>
       <c r="D13" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="F13" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="G13" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="H13" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="I13" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="J13" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="K13" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="K13" s="11" t="s">
+    </row>
+    <row r="14" spans="1:11" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
-        <v>133</v>
-      </c>
       <c r="B14" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>38</v>
       </c>
       <c r="D14" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="F14" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="G14" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="H14" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="I14" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="J14" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="K14" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="K14" s="11" t="s">
+    </row>
+    <row r="15" spans="1:11" ht="150" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
-        <v>142</v>
-      </c>
       <c r="B15" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>40</v>
       </c>
       <c r="D15" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="F15" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="G15" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="H15" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="I15" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="J15" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="K15" s="11" t="s">
         <v>149</v>
-      </c>
-      <c r="K15" s="11" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2029,178 +2027,178 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+    </row>
+    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="26" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-    </row>
-    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
     </row>
     <row r="3" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="D3" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>157</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="D4" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="E4" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="F4" s="16" t="s">
         <v>162</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="D5" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="E5" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="F5" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="F5" s="16" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="32" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="B8" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="C8" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="C8" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="30"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
     </row>
     <row r="9" spans="1:6" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="C9" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="C9" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
     </row>
     <row r="10" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B10" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C10" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="C10" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="C11" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="C11" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
     </row>
     <row r="12" spans="1:6" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="C12" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:6" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="C13" s="25" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="9">
